--- a/data/trans_orig/Q64C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que trabaja a la semana</t>
+          <t>Número medio de horas que trabaja a la semana (tasa de respuesta: 97,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,05; 41,19</t>
+          <t>39,09; 41,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,06; 42,62</t>
+          <t>39,8; 42,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,62; 38,59</t>
+          <t>35,59; 38,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,77; 39,6</t>
+          <t>37,77; 39,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,9; 37,32</t>
+          <t>34,81; 37,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,43; 38,41</t>
+          <t>35,41; 38,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 35,45</t>
+          <t>32,6; 35,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 36,9</t>
+          <t>35,16; 36,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 39,29</t>
+          <t>37,72; 39,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,49; 40,72</t>
+          <t>38,41; 40,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,59; 36,7</t>
+          <t>34,62; 36,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,84; 38,07</t>
+          <t>36,88; 38,13</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,12; 38,9</t>
+          <t>37,03; 38,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,69; 40,64</t>
+          <t>38,67; 40,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 39,94</t>
+          <t>37,92; 40,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,85</t>
+          <t>36,61; 38,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,76; 37,09</t>
+          <t>34,67; 36,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,84; 36,35</t>
+          <t>33,72; 36,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,28; 36,08</t>
+          <t>33,17; 36,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,1; 36,26</t>
+          <t>34,23; 36,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 37,78</t>
+          <t>36,22; 37,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,69</t>
+          <t>37,05; 38,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,12; 37,9</t>
+          <t>36,2; 37,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,8; 37,38</t>
+          <t>35,87; 37,4</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,35; 43,68</t>
+          <t>41,37; 43,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,03; 45,4</t>
+          <t>43,04; 45,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,92; 43,24</t>
+          <t>39,84; 43,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 42,12</t>
+          <t>12,61; 42,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,72; 42,4</t>
+          <t>37,67; 42,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,19; 44,86</t>
+          <t>40,14; 44,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,93; 42,09</t>
+          <t>36,62; 41,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,69; 40,12</t>
+          <t>35,81; 39,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,04; 43,34</t>
+          <t>41,14; 43,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,56; 44,71</t>
+          <t>42,59; 44,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,68; 42,51</t>
+          <t>39,5; 42,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 41,24</t>
+          <t>14,1; 41,23</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,75; 43,18</t>
+          <t>41,73; 43,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,23; 42,03</t>
+          <t>40,17; 42,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 41,36</t>
+          <t>39,54; 41,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 41,84</t>
+          <t>40,04; 41,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,19; 41,36</t>
+          <t>38,18; 41,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,17; 36,94</t>
+          <t>34,08; 36,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,94; 37,91</t>
+          <t>34,94; 37,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,63; 37,29</t>
+          <t>35,61; 37,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,93; 42,45</t>
+          <t>40,96; 42,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,01; 39,68</t>
+          <t>37,98; 39,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,85; 39,53</t>
+          <t>37,84; 39,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,39; 39,57</t>
+          <t>38,38; 39,55</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,93; 41,11</t>
+          <t>37,76; 41,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,83; 41,02</t>
+          <t>37,85; 40,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,26; 39,99</t>
+          <t>37,21; 40,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,85; 40,19</t>
+          <t>37,77; 40,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,17; 37,07</t>
+          <t>33,32; 37,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,42; 33,24</t>
+          <t>29,51; 33,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,45</t>
+          <t>29,96; 33,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,23; 34,35</t>
+          <t>26,19; 34,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 38,44</t>
+          <t>35,76; 38,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,77; 36,3</t>
+          <t>33,63; 36,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 36,28</t>
+          <t>34,09; 36,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,43</t>
+          <t>29,67; 36,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1348,62 +1348,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41,14</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41,25</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39,44</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35,67</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37,13</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35,84</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34,91</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34,85</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39,73</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39,08</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37,52</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35,32</t>
         </is>
       </c>
     </row>
@@ -1416,221 +1416,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,66; 41,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,76; 41,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,88; 40,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,07; 39,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,41; 37,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,06; 36,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,16; 35,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,5; 35,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,35; 40,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,59; 39,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,07; 38,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,29; 37,73</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>41,14</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41,25</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39,44</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35,67</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37,13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,84</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,91</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34,85</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>39,73</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>39,08</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37,52</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,32</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>40,7; 41,62</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40,71; 41,75</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38,84; 40,02</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23,28; 39,88</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,34; 37,83</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,07; 36,69</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,14; 35,68</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32,5; 35,76</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39,33; 40,15</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>38,67; 39,51</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>37,03; 37,99</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>27,3; 37,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>

--- a/data/trans_orig/Q64C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,69</t>
+          <t>38,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,1</t>
+          <t>35,79</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,46</t>
+          <t>37,17</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,09; 41,13</t>
+          <t>39,08; 41,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,8; 42,5</t>
+          <t>40,0; 42,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,59; 38,41</t>
+          <t>35,57; 38,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,77; 39,62</t>
+          <t>37,55; 39,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,81; 37,25</t>
+          <t>34,9; 37,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,41; 38,43</t>
+          <t>35,29; 38,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 35,35</t>
+          <t>32,54; 35,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,16; 36,87</t>
+          <t>34,9; 36,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 39,31</t>
+          <t>37,8; 39,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 40,5</t>
+          <t>38,57; 40,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,62; 36,65</t>
+          <t>34,64; 36,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,88; 38,13</t>
+          <t>36,55; 37,77</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,86</t>
+          <t>37,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,32</t>
+          <t>35,27</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,71</t>
+          <t>36,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 38,91</t>
+          <t>37,15; 38,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,76</t>
+          <t>38,71; 40,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,92; 40,02</t>
+          <t>37,83; 39,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,61; 38,72</t>
+          <t>36,68; 38,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 36,94</t>
+          <t>34,69; 37,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,72; 36,44</t>
+          <t>33,81; 36,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17; 36,1</t>
+          <t>33,19; 35,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 36,25</t>
+          <t>34,18; 36,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,22; 37,77</t>
+          <t>36,35; 37,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,68</t>
+          <t>37,1; 38,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 37,84</t>
+          <t>36,12; 37,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,87; 37,4</t>
+          <t>35,95; 37,42</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,72</t>
+          <t>41,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,95</t>
+          <t>38,54</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,33</t>
+          <t>41,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,37; 43,8</t>
+          <t>41,27; 43,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,04; 45,37</t>
+          <t>42,95; 45,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,84; 43,43</t>
+          <t>39,74; 43,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 42,19</t>
+          <t>40,69; 43,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,32</t>
+          <t>37,75; 42,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,14; 44,73</t>
+          <t>40,3; 44,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 41,64</t>
+          <t>36,93; 42,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,81; 39,98</t>
+          <t>36,32; 40,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,14; 43,41</t>
+          <t>41,04; 43,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,59; 44,77</t>
+          <t>42,71; 44,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 42,38</t>
+          <t>39,7; 42,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 41,23</t>
+          <t>40,03; 42,29</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,89</t>
+          <t>41,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,49</t>
+          <t>36,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,97</t>
+          <t>38,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,73; 43,2</t>
+          <t>41,77; 43,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 42,0</t>
+          <t>40,15; 41,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,54; 41,55</t>
+          <t>39,53; 41,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,04; 41,7</t>
+          <t>40,31; 41,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,18; 41,31</t>
+          <t>38,17; 41,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 36,98</t>
+          <t>34,12; 37,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,94; 37,79</t>
+          <t>34,96; 37,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,61; 37,24</t>
+          <t>35,35; 37,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,96; 42,35</t>
+          <t>41,0; 42,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,98; 39,64</t>
+          <t>37,91; 39,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,84; 39,59</t>
+          <t>37,86; 39,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,38; 39,55</t>
+          <t>38,36; 39,54</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,11</t>
+          <t>39,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,01</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>36,39</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,76; 41,1</t>
+          <t>37,89; 41,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,85; 40,84</t>
+          <t>37,81; 40,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,21; 40,06</t>
+          <t>37,15; 39,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,77; 40,19</t>
+          <t>38,59; 40,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,32; 37,08</t>
+          <t>33,06; 37,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 33,15</t>
+          <t>29,63; 33,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 33,52</t>
+          <t>30,29; 33,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,19; 34,22</t>
+          <t>32,08; 34,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,39</t>
+          <t>35,81; 38,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,63; 36,28</t>
+          <t>33,67; 36,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,09; 36,47</t>
+          <t>34,02; 36,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,67; 36,27</t>
+          <t>35,59; 37,17</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,67</t>
+          <t>39,88</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,85</t>
+          <t>35,44</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,32</t>
+          <t>37,93</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,66; 41,6</t>
+          <t>40,68; 41,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,76; 41,78</t>
+          <t>40,77; 41,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,88; 40,07</t>
+          <t>38,87; 40,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,07; 39,9</t>
+          <t>39,42; 40,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,41; 37,96</t>
+          <t>36,34; 37,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,06; 36,56</t>
+          <t>35,09; 36,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,16; 35,68</t>
+          <t>34,06; 35,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,5; 35,81</t>
+          <t>34,97; 35,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,35; 40,12</t>
+          <t>39,3; 40,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,51</t>
+          <t>38,6; 39,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,07; 38,02</t>
+          <t>37,02; 37,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,29; 37,73</t>
+          <t>37,59; 38,25</t>
         </is>
       </c>
     </row>
